--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Codeguardian Tech International Pvt Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=2351c626fcc056a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior AI/ML engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bda8473faa56bc21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Artificial Intelligence Engineer Fresher</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pontiac, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, S3, EC2, Databricks, NoSQL, Tableau, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3918f64feb6d441</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2b4f423b5aa48d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer, Consultant</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1bf6e8fe7753af</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Core Infrastructure</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Jenkins, Snowflake, Databricks, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9630c80cb512c4c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Core Infrastructure</t>
+          <t>Data Scientist 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Olathe, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, NoSQL, Dask, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf88e54d8fe83e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e178364f05e3b1b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Core Infrastructure</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Synapse, CI/CD, Git, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,182 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a343a564a678782b</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Core Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Dask, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90ebb1bdfce09eb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Diagnostics Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b627d9b98e97fc28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Synapse, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50adecff053ae72d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist I supporting social science research, analytics, and AI initiatives</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NORC at the University of Chicago</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e175c3cdc8c78d03</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9277f5fa9d5a553c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, BigQuery, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codeguardian Tech International Pvt Ltd.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2351c626fcc056a6</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI/ML engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Cortex, Apache Airflow, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda8473faa56bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer Fresher</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>TensorFlow, PyTorch, Keras, S3, EC2, Databricks, NoSQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2b4f423b5aa48d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c327ff07e711acf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Programmer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Statewide Monitoring Corp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,287 +636,77 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6323181ce5f2b7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Qodo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Jenkins, Snowflake, Databricks, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=18f8177cb139dba7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist 2</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Qodo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Olathe, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, NoSQL, Dask, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e178364f05e3b1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Synapse, CI/CD, Git, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Atlassian</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Dask, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90ebb1bdfce09eb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Diagnostics Software Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b627d9b98e97fc28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Synapse, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50adecff053ae72d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist I supporting social science research, analytics, and AI initiatives</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NORC at the University of Chicago</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9277f5fa9d5a553c</t>
+          <t>https://www.indeed.com/viewjob?jk=143f9fcb8cc2f2d5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, BigQuery, MLflow, FastAPI, Docker</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Azure ML, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward-Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, TensorFlow, PyTorch, FastAPI, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,54 +531,54 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=df5ee7b52556180b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Apache Airflow, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Sr Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, S3, EC2, Databricks, NoSQL, Tableau, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c327ff07e711acf</t>
+          <t>https://www.indeed.com/viewjob?jk=de4cd96625f43126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Programmer</t>
+          <t>Forward Deployed Engineer IV - US</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Statewide Monitoring Corp</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6323181ce5f2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2acf5038448d3893</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qodo</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Glue, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,672 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f8177cb139dba7</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qodo</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ServiceNow AI Architect (ServiceNow AI Implementation)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Clearpath Development LLC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07153149b3ca09bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git, Redshift</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mastronardi Produce</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Livonia, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cloud DB Architect / ML &amp; Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bryan Knuff &amp; Associates CPAs PA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Eagle, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9da20ea629da8e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Architect - Clinical Domain</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f22ea189caa4780</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc87b1d33484b430</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a65d2a25a2f2570e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Engineer - Application</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vallen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Belmont, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Data Lake, MLflow, CI/CD, Databricks, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bd480315d8b4619</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Meijer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f16ad24f847cd81</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MOLG</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39afd91a4e243b1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21ad849fd07eb27c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Skyflow</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=143f9fcb8cc2f2d5</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BigQuery, Snowflake, BigQuery, Kafka, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60e9e41c50d42989</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d576fb280869f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Aventura, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b610b43f78cc9adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f4be6c1486f6acb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=378d6f05aef8158c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dbbc8df619f059d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Azure ML, Docker, Kubernetes, Git</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward-Deployed Engineer (FDE)</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, TensorFlow, PyTorch, FastAPI, Git</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, BigQuery, Dataflow, Docker, Jenkins, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df5ee7b52556180b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Associate AI &amp; Data Consultat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b23b4bfbd9797ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4cd96625f43126</t>
+          <t>https://www.indeed.com/viewjob?jk=7a272c809bfda372</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer IV - US</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
+          <t>S3, EC2, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acf5038448d3893</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, CI/CD, Jenkins, Snowflake, Databricks, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Senior AI Engineer - Virtual</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, Glue, CI/CD, Jenkins, Git, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=0e517e629dfbc725</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ServiceNow AI Architect (ServiceNow AI Implementation)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clearpath Development LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, Git, Snowflake, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07153149b3ca09bf</t>
+          <t>https://www.indeed.com/viewjob?jk=94f0fe563cadd680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git, Redshift</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Engineer / SDET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6069cb06d83352</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud DB Architect / ML &amp; Agentic AI Engineer</t>
+          <t>AI/ML Observability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bryan Knuff &amp; Associates CPAs PA</t>
+          <t>Stradit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, CI/CD, Snowflake, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da20ea629da8e03</t>
+          <t>https://www.indeed.com/viewjob?jk=e926b6a01c0abd91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Architect - Clinical Domain</t>
+          <t>AI/ML Observability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Stradit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, CI/CD, Snowflake, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f22ea189caa4780</t>
+          <t>https://www.indeed.com/viewjob?jk=999731d2d66ddf42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Client Partner – Cloud Data Platforms &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Waterloo Data</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc87b1d33484b430</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb258684500991e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ubiety</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65d2a25a2f2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer - Application</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vallen</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belmont, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Data Lake, MLflow, CI/CD, Databricks, Power BI, Python, SQL</t>
+          <t>S3, Glue, Redshift, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd480315d8b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meijer</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f16ad24f847cd81</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. SW Engineer. Software Engineering-2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MOLG</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39afd91a4e243b1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a077a7f23606122e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Scientist I/II (Remote - US)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BNSF Railway</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Git, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ad849fd07eb27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9de453aff01c09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Skyflow</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BigQuery, Snowflake, BigQuery, Kafka, MongoDB, Python, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e9e41c50d42989</t>
+          <t>https://www.indeed.com/viewjob?jk=94e6ad0ece5355c3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Sr. Engineer, Data Governance &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d576fb280869f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fa189724d3d82d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b610b43f78cc9adf</t>
+          <t>https://www.indeed.com/viewjob?jk=07b63c559df37861</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, AKS, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4be6c1486f6acb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f78e1ce621ad9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Research Software Engineer I - Center for AI and Research Computing (AIRC)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Salk Institute for Biological Studies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378d6f05aef8158c</t>
+          <t>https://www.indeed.com/viewjob?jk=30fba370c820cb53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,192 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>RAG, AKS, CI/CD, Snowflake, Power BI, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b40e6272e71b5bdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, S3, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72f228fff874be16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Modus Closing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Aventura, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dbbc8df619f059d</t>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f8369bf3160375a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineering Consultant (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Securian Financial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9118aee40c8d2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AWS Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Athena, Redshift, Redshift, Quicksight, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b1dc509b9bd937c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PRADCO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6a5ebca6556fdef</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>Generative AI, RAG, Glue, Athena, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, BigQuery, Dataflow, Docker, Jenkins, Git, BigQuery</t>
+          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate AI &amp; Data Consultat</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b23b4bfbd9797ff</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a272c809bfda372</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Sr Software Engineer - Database Systems</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
+          <t>BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=34f0a1670e8fc5e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Jenkins, Snowflake, Databricks, Kafka, Python, R</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d55d4ffe7a3232</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Virtual</t>
+          <t>Senior Engineer (Golang)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, Glue, CI/CD, Jenkins, Git, PySpark</t>
+          <t>RAG, Kubernetes, CI/CD, Git, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e517e629dfbc725</t>
+          <t>https://www.indeed.com/viewjob?jk=daaee8eeaa1d9772</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, Git, Snowflake, Power BI, Python</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f0fe563cadd680</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Analytics Engineer, Business Solutions</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Vertex Service Partners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=254a42e48d7efee2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sutter Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Azure ML, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=420992c7d2dfef21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QA Engineer / SDET</t>
+          <t>Software Engineer, Dev Tools</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6069cb06d83352</t>
+          <t>https://www.indeed.com/viewjob?jk=d425b215fde16720</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Observability Engineer</t>
+          <t>Analytics Engineer, Life Sciences Delivery Operations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stradit</t>
+          <t>Arcadia.io</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, CI/CD, Snowflake, Matplotlib, Seaborn</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Git, Snowflake, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e926b6a01c0abd91</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a33ed7e215e05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Observability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stradit</t>
+          <t>Well Dot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chapel Hill, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, CI/CD, Snowflake, Matplotlib, Seaborn</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Terraform, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999731d2d66ddf42</t>
+          <t>https://www.indeed.com/viewjob?jk=5641ff0e90d249bc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Client Partner – Cloud Data Platforms &amp; AI</t>
+          <t>Pricing Strategy and Data Science Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Waterloo Data</t>
+          <t>Daimler Truck North America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb258684500991e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc7e447327f6936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Post-Doctoral Fellow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ubiety</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87771f60adaa39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Post-Doctoral Fellow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Redshift</t>
+          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=06c2ca38f04c7062</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Post-Doctoral Fellow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Kafka, Hadoop, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=22d8191ef742e0c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer. Software Engineering-2</t>
+          <t>Application Security Engineer – Software Composition Analysis (SCA)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Zelis Healthcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a077a7f23606122e</t>
+          <t>https://www.indeed.com/viewjob?jk=68293857546a8835</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist I/II (Remote - US)</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BNSF Railway</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9de453aff01c09</t>
+          <t>https://www.indeed.com/viewjob?jk=1d29aeac265e72fb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Developer Experience Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Picogrid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e6ad0ece5355c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8531d6e59bdeb010</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data Governance &amp; AI Enablement</t>
+          <t>AI Ops Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fa189724d3d82d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdfdcb301ffaa57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer/DBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>TRUITY CREDIT UNION</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,301 +1217,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>Jenkins, Snowflake, MySQL, MongoDB, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b63c559df37861</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, AKS, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f78e1ce621ad9</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Research Software Engineer I - Center for AI and Research Computing (AIRC)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Salk Institute for Biological Studies</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>La Jolla, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30fba370c820cb53</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, AKS, CI/CD, Snowflake, Power BI, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b40e6272e71b5bdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Pinecone, S3, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72f228fff874be16</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Modus Closing</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Aventura, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8369bf3160375a</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Engineering Consultant (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Securian Financial</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9118aee40c8d2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AWS Data Scientist</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, Redshift, Quicksight, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1dc509b9bd937c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PRADCO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, MLflow, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a5ebca6556fdef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1b0ce6ab642f1c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-21.xlsx
+++ b/daily_matches/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, Athena, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=439377efddb3496b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc6276c79dcfd60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf953a2c9ee5bf5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Database Systems</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Synapse, MLflow, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f0a1670e8fc5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, FAISS, Pinecone, TensorFlow, PyTorch, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d55d4ffe7a3232</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer (Golang)</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaee8eeaa1d9772</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Auto Finance Platform Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee1b00bfc5bcc2a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Business Solutions</t>
+          <t>Auto Finance Platform Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vertex Service Partners</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254a42e48d7efee2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddfc5fc0c2d50b7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Auto Finance Platform Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sutter Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Azure ML, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=420992c7d2dfef21</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6fb261ea505668</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Dev Tools</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,137 +846,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d425b215fde16720</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Life Sciences Delivery Operations</t>
+          <t>ML/AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arcadia.io</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Git, Snowflake, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a33ed7e215e05</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a907385d6f8926</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Well Dot</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Terraform, BigQuery, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5641ff0e90d249bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pricing Strategy and Data Science Analyst</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Daimler Truck North America</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc7e447327f6936</t>
+          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellow</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87771f60adaa39</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellow</t>
+          <t>Full Stack Web Developer (React / Vue / Laravel / Node / Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>UpPoint, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
+          <t>Copilot, S3, FastAPI, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c2ca38f04c7062</t>
+          <t>https://www.indeed.com/viewjob?jk=293a428f98b647e3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellow</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d8191ef742e0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=02df338251cd6b6a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Application Security Engineer – Software Composition Analysis (SCA)</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zelis Healthcare</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68293857546a8835</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Splitero</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d29aeac265e72fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f463e8412c264ae4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Developer Experience Engineer</t>
+          <t>Full Stack Software Engineer (2–3 Years Experience)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Picogrid</t>
+          <t>ramtech Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, S3, Docker, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8531d6e59bdeb010</t>
+          <t>https://www.indeed.com/viewjob?jk=a98058924d43093e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Ops Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Omnidian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,427 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdfdcb301ffaa57</t>
+          <t>https://www.indeed.com/viewjob?jk=c391673b5f400fae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TRUITY CREDIT UNION</t>
+          <t>Tower Research Capital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=415cd67055128a58</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer- Infrastructure</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>New Relic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3b26711bef4b24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deltek</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=446891004394dd6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d0d377d16857513</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Technical Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BigQuery, Docker, CI/CD, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea28edb6897859ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Technical Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BigQuery, Docker, CI/CD, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ccf0e037b2286ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer I – AI Applications</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mears Group Inc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e57f59030cf5cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Account Engineer - Public Sector/SLED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jenkins, Snowflake, MySQL, MongoDB, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1b0ce6ab642f1c</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ffbf49742095198</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EdgeBeam Wireless</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6af63a3bf6cf834</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deltek</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Snowflake, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c05f40ae180c4f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4eccae0fb130e8</t>
         </is>
       </c>
     </row>
